--- a/automation/reports/Excel/Execution_Summary.xlsx
+++ b/automation/reports/Excel/Execution_Summary.xlsx
@@ -35,7 +35,7 @@
     <t>Overall Pass Rate</t>
   </si>
   <si>
-    <t>98.82%</t>
+    <t>100.00%</t>
   </si>
 </sst>
 </file>
@@ -117,7 +117,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>510.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="3">
@@ -125,7 +125,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>504.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="4">
@@ -133,7 +133,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -141,7 +141,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">

--- a/automation/reports/Excel/Execution_Summary.xlsx
+++ b/automation/reports/Excel/Execution_Summary.xlsx
@@ -117,7 +117,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>320.0</v>
+        <v>310.0</v>
       </c>
     </row>
     <row r="3">
@@ -125,7 +125,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>320.0</v>
+        <v>310.0</v>
       </c>
     </row>
     <row r="4">

--- a/automation/reports/Excel/Execution_Summary.xlsx
+++ b/automation/reports/Excel/Execution_Summary.xlsx
@@ -117,7 +117,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>310.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="3">
@@ -125,7 +125,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>310.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="4">

--- a/automation/reports/Excel/Execution_Summary.xlsx
+++ b/automation/reports/Excel/Execution_Summary.xlsx
@@ -6,36 +6,51 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary Metrics" r:id="rId3" sheetId="1"/>
+    <sheet name="Execution Summary" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Metric Category</t>
-  </si>
-  <si>
-    <t>Count / Value</t>
-  </si>
-  <si>
-    <t>Total Scenarios</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>Overall Pass Rate</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Total Test Cases</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Passed Tests</t>
+  </si>
+  <si>
+    <t>Failed Tests</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
   </si>
   <si>
     <t>100.00%</t>
+  </si>
+  <si>
+    <t>Execution Status</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Android / Web / Security Live Automation</t>
   </si>
 </sst>
 </file>
@@ -67,16 +82,16 @@
     </fill>
     <fill>
       <patternFill patternType="none">
-        <fgColor indexed="63"/>
+        <fgColor indexed="18"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="63"/>
+        <fgColor indexed="18"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -84,27 +99,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFill="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.70703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.26953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.21875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.5390625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24.0" customHeight="true">
       <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
@@ -112,44 +146,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" ht="20.0" customHeight="true">
+      <c r="A2" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>300.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="B2" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>300.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    </row>
+    <row r="3" ht="20.0" customHeight="true">
+      <c r="A3" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
+      <c r="B3" t="s" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="20.0" customHeight="true">
+      <c r="A4" t="s" s="2">
         <v>5</v>
       </c>
-      <c r="B5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
+      <c r="B4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B6" t="s" s="0">
+    </row>
+    <row r="5" ht="20.0" customHeight="true">
+      <c r="A5" t="s" s="2">
         <v>7</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="20.0" customHeight="true">
+      <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="20.0" customHeight="true">
+      <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
